--- a/public/menu_template.xlsx
+++ b/public/menu_template.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
-    <t>name</t>
+    <t>dish</t>
   </si>
   <si>
     <t>category</t>
@@ -87,7 +87,7 @@
     <t>Columns</t>
   </si>
   <si>
-    <t>name (required) — the name customers see and search for.</t>
+    <t>dish (required) — the name customers see and search for.</t>
   </si>
   <si>
     <t>category — used to group items (e.g. Bouquets, Starters). Optional but recommended.</t>
@@ -132,7 +132,7 @@
     <t>Columnas</t>
   </si>
   <si>
-    <t>name (obligatorio) — el nombre que ven y buscan los clientes.</t>
+    <t>dish (obligatorio) — el nombre que ven y buscan los clientes.</t>
   </si>
   <si>
     <t>category — agrupa los ítems (ej: Ramos, Entradas). Opcional pero recomendado.</t>
